--- a/db/templates/incoming_invoice_tunisia.xlsx
+++ b/db/templates/incoming_invoice_tunisia.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
   <si>
     <t>{{organization.logo}}</t>
   </si>
@@ -59,6 +59,9 @@
     <t>Date : {{incomingInvoice.date}}</t>
   </si>
   <si>
+    <t>Code</t>
+  </si>
+  <si>
     <t>Désignation</t>
   </si>
   <si>
@@ -71,6 +74,9 @@
     <t>TOTAL HT</t>
   </si>
   <si>
+    <t>{{lineItems.sku}}</t>
+  </si>
+  <si>
     <t>{{lineItems.description}}</t>
   </si>
   <si>
@@ -300,6 +306,9 @@
   </si>
   <si>
     <t>Marker (not a value) — place alone in one cell of the row to repeat once per line item</t>
+  </si>
+  <si>
+    <t>Linked product's SKU (the Code column), blank on a free-text line</t>
   </si>
   <si>
     <t>Line item description</t>
@@ -776,7 +785,7 @@
   <cols>
     <col customWidth="true" max="1" min="1" width="14"/>
     <col customWidth="true" max="2" min="2" width="34"/>
-    <col customWidth="true" max="4" min="3" width="16"/>
+    <col customWidth="true" max="5" min="3" width="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -874,80 +883,86 @@
       <c r="D11" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="E11" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="5" t="s">
         <v>18</v>
       </c>
+      <c r="B12" s="7" t="s">
+        <v>19</v>
+      </c>
       <c r="C12" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="J12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="D17" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24">
       <c r="D24" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -982,28 +997,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
@@ -1011,55 +1026,55 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
@@ -1067,87 +1082,87 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24">
@@ -1155,166 +1170,166 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="s">
-        <v>100</v>
+      <c r="B39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" t="s">
-        <v>101</v>
+      <c r="A40" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="s">
-        <v>105</v>
+      <c r="B44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="s">
-        <v>30</v>
-      </c>
-      <c r="C45" t="s">
-        <v>106</v>
+      <c r="A45" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="46">
@@ -1322,7 +1337,7 @@
         <v>32</v>
       </c>
       <c r="C46" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47">
@@ -1330,44 +1345,52 @@
         <v>34</v>
       </c>
       <c r="C47" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="C48" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="s">
-        <v>111</v>
+      <c r="B49" t="s">
+        <v>112</v>
+      </c>
+      <c r="C49" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="s">
-        <v>112</v>
-      </c>
-      <c r="C50" t="s">
-        <v>113</v>
+      <c r="A50" s="11" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C51" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C52" t="s">
-        <v>117</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -1375,9 +1398,9 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A50:C50"/>
   </mergeCells>
 </worksheet>
 </file>